--- a/artfynd/A 47653-2024 artfynd.xlsx
+++ b/artfynd/A 47653-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3981953</v>
+        <v>62602283</v>
       </c>
       <c r="B2" t="n">
-        <v>99589</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221333</v>
+        <v>448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Mjölspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Cortinarius flavovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skadevi,Skokloster, Upl</t>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641994.9337757325</v>
+        <v>642075</v>
       </c>
       <c r="R2" t="n">
-        <v>6618672.470853616</v>
+        <v>6618658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Mellan Skadevi och grusgropen</t>
+          <t>2 ex. i gles vegetation av bl.a. blåsippa, under ek och hassel i lövskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,68 +773,72 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägren</t>
+          <t>Lövskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thommy Åkerberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thommy Åkerberg, Michael Åkerberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2623269</v>
+        <v>62602284</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Mjölspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius flavovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skadevi,Skokloster, Upl</t>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641994.9337757325</v>
+        <v>642155</v>
       </c>
       <c r="R3" t="n">
-        <v>6618672.470853616</v>
+        <v>6618619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,27 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2003-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lunden väster Skadevi</t>
+          <t>2 ex. i gles vegetation under hassel och ek. Tydlig lukt av mjöl.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,73 +889,72 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Lövskog, med ek, hassel och björk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thommy Åkerberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thommy Åkerberg, Michael Åkerberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5030670</v>
+        <v>62602285</v>
       </c>
       <c r="B4" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>448</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mjölspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius flavovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skadevi, Upl</t>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>642054.5333576386</v>
+        <v>642166</v>
       </c>
       <c r="R4" t="n">
-        <v>6618703.044497491</v>
+        <v>6618609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,22 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-04-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-04-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 ex. under ek, björk och hassel i lövskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,21 +1005,2259 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lövskogslund</t>
+          <t>Lövskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62602286</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87253</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>448</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mjölspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius flavovirens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>642169</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618604</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 ex. på bar jord under ek och hassel i lövskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövskog, med ek, hassel och björk.</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69509175</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87310</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>450</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Saffransspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius olearioides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>642165</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618624</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-09-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-09-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. under ek och hassel.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövskog, med ek, hassel och björk.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>69509177</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87310</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>450</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Saffransspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius olearioides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>642090</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618653</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 äldre ex. i gles vegetation under ek och hassel i lövskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>58512855</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89105</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>806</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Luktvaxing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hygrocybe quieta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>642085</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618698</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. på bar jord under ek, alm och hassel i lövskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>58512856</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89105</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>806</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Luktvaxing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hygrocybe quieta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>642116</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618649</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex. under ek och hassel i lövskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>58512857</v>
+      </c>
+      <c r="B10" t="n">
+        <v>89105</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>806</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Luktvaxing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hygrocybe quieta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>642157</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6618626</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex. i gles vegetation under ek och hassel i lövskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>61804743</v>
+      </c>
+      <c r="B11" t="n">
+        <v>88430</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1009</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Slöjröksvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycoperdon mammiforme</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>642151</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6618629</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2011-09-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2011-09-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 ex. i gles vegetation, intill en sten, under hassel, ek och björk.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövskog, med ek, hassel och björk.</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>62601632</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92613</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Prakttagging</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Steccherinum robustius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>641983</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6618581</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2009-02-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2009-02-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>7 dm2 på bark på stammen av död, stående alm (almsjukedödat träd), omkr. 127 cm.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog.</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark på stammen av död, stående alm. # Skogsalm</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62601633</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92613</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Prakttagging</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Steccherinum robustius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>641986</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6618577</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2009-02-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2009-02-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5 dm2 på bark på stammen av död, stående alm (almsjukedödat träd), omkr. 109 cm.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog.</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark på stammen av död, stående alm. # Skogsalm</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>62601634</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92613</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Prakttagging</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Steccherinum robustius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>642015</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6618519</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2009-02-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2009-02-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>20 dm2 på bark på almlåga, omkr. 122 cm.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog.</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark på almlåga. # Skogsalm</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111435280</v>
+      </c>
+      <c r="B15" t="n">
+        <v>89922</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1669</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grå vedslidskivling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Volvariella caesiotincta</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>P. D. Orton</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ekenäs, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>642083</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6618511</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hatt c 30–75 mm bred, strumpa mörkgrå, cystider med utdragen spets. Jfr Antonin, V. (2012) Some taxonomic and ecological notes om Volvariella caesiotincta. Acta Musei Moraviae 97 (2): 87-99.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ädellövskog med ask, alm, ek, hassel, gran etc</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Murkna vedrester, troligen av gran och ask/alm</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>62602298</v>
+      </c>
+      <c r="B16" t="n">
+        <v>81655</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3929</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Läderskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Encoelia furfuracea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Roth.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>642094</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6618700</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På liggande hasselstam.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ek-/hassellund.</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Hassel</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Hassellåga. # Hassel</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>59720343</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90312</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4037</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bolmörtsskivling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Entoloma sinuatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Bull.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>642166</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6618609</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. under ek och hassel.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>59720345</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90312</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4037</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bolmörtsskivling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Entoloma sinuatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Bull.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>642088</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6618697</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2008-09-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca. 15 ex. på bar jord under ek, alm och hassel.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2623269</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skadevi,Skokloster, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>641995</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6618672</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2003-12-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Lunden väster Skadevi</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Thommy Åkerberg</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thommy Åkerberg, Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>62602273</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>642065</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6618683</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2002-01-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2002-01-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10 vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>62602276</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Eknäs NV om Häggeby kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>642099</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6618744</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>6 vinterståndare i ek-/hassellund.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Ek-/hassellund.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3981953</v>
+      </c>
+      <c r="B22" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skadevi,Skokloster, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>641995</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6618672</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2003-12-31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mellan Skadevi och grusgropen</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
         <is>
           <t>Thommy Åkerberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thommy Åkerberg, Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5030670</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skadevi, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>642055</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6618703</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häggeby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2007-04-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2007-04-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Lövskogslund</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Thommy Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Thommy Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47653-2024 artfynd.xlsx
+++ b/artfynd/A 47653-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62602283</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62602284</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62602285</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62602286</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69509175</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69509177</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58512855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1606,6 +1646,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58512856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1722,6 +1767,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58512857</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1844,6 +1894,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61804743</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1970,6 +2025,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62601632</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2096,6 +2156,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62601633</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2222,6 +2287,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62601634</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2346,6 +2416,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111435280</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2463,6 +2538,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62602298</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2579,6 +2659,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59720343</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2695,6 +2780,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59720345</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2802,6 +2892,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2623269</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2923,6 +3018,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62602273</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3044,6 +3144,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62602276</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3151,6 +3256,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3981953</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3258,8 +3368,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5030670</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>